--- a/artfynd/A 26438-2026 artfynd.xlsx
+++ b/artfynd/A 26438-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925267</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133925266</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26438-2026 artfynd.xlsx
+++ b/artfynd/A 26438-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133925267</v>
+        <v>133925266</v>
       </c>
       <c r="B2" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755615</v>
+        <v>755453</v>
       </c>
       <c r="R2" t="n">
-        <v>7331189</v>
+        <v>7331186</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133925266</v>
+        <v>133925267</v>
       </c>
       <c r="B3" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755453</v>
+        <v>755615</v>
       </c>
       <c r="R3" t="n">
-        <v>7331186</v>
+        <v>7331189</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 26438-2026 artfynd.xlsx
+++ b/artfynd/A 26438-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>